--- a/.cursor/scratch/tax_turbo_parts/Personal Income 2025.labeled.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/Personal Income 2025.labeled.xlsx
@@ -642,7 +642,7 @@
         <v>20000</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>39055.06</v>
+        <v>24055.06</v>
       </c>
     </row>
     <row r="9">
@@ -3039,7 +3039,7 @@
         <v>14000</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>136000</v>
+        <v>121000</v>
       </c>
       <c r="D53" s="1" t="n">
         <v>0</v>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="D54" s="1" t="n">
         <v>0</v>
@@ -3095,28 +3095,28 @@
         <v>0</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="G54" s="1" t="n">
         <v>13595</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>0</v>
+        <v>11034.79</v>
       </c>
       <c r="I54" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>0</v>
+        <v>14161.27</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="L54" s="1" t="n">
         <v>0</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>0</v>
+        <v>4700.26</v>
       </c>
       <c r="N54" s="1">
         <f>SUM(B54:M54)</f>
@@ -3798,7 +3798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K81"/>
+  <dimension ref="A1:K82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -4958,70 +4958,80 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Two mosaic deals (EOEB 2/21 pooled)</t>
+          <t>Mosaic Deal B — Plutus/Antiquarium</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Jamal Rifai (Deal A) + Plutus/Antiquarium (Deal B)</t>
+          <t>Plutus &amp; Mnemosyne / DBA Antiquarium</t>
         </is>
       </c>
       <c r="C74" s="1" t="n">
-        <v>90000</v>
+        <v>50000</v>
       </c>
       <c r="F74" s="1" t="n">
-        <v>105000</v>
+        <v>50000</v>
       </c>
       <c r="H74" s="1">
-        <f>SUM(F74-C74)</f>
-        <v/>
+        <f>F74-C74</f>
+        <v/>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>SALE</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Canosan Terracotta Horse</t>
+          <t>Mosaic Deal A — Three Ancient Mosaics / Jamal Rifai</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Hindman</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="n">
-        <v>900</v>
+          <t>Jamal M. Rifai (Cost ASK — personal BoA)</t>
+        </is>
       </c>
       <c r="F75" s="1" t="n">
-        <v>1000</v>
+        <v>40000</v>
       </c>
       <c r="H75" s="1">
-        <f>SUM(F75-C75)</f>
-        <v/>
+        <f>IF(OR(F75="",C75=""),"",F75-C75)</f>
+        <v/>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>SALE</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Sale 6428 Contract 303468 (object TBD)</t>
+          <t>Canosan Terracotta Horse</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Cost TBD</t>
-        </is>
+          <t>Hindman</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="n">
+        <v>900</v>
       </c>
       <c r="F76" s="1" t="n">
-        <v>11000</v>
+        <v>1000</v>
       </c>
       <c r="H76" s="1">
-        <f>IF(C76="","",F76-C76)</f>
+        <f>SUM(F76-C76)</f>
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Books (titles TBD)</t>
+          <t>Sale 6428 Contract 303468 (object TBD)</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -5030,44 +5040,36 @@
         </is>
       </c>
       <c r="F77" s="1" t="n">
-        <v>1000</v>
+        <v>11000</v>
       </c>
       <c r="H77" s="1">
-        <f>IF(OR(F77="",C77=""),"",F77-C77)</f>
+        <f>IF(C77="","",F77-C77)</f>
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Roman Gold Belt</t>
+          <t>Books (titles TBD)</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Fortuna / Erdal Dere</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="n">
-        <v>45000</v>
+          <t>Cost TBD</t>
+        </is>
       </c>
       <c r="F78" s="1" t="n">
-        <v>50000</v>
+        <v>1000</v>
       </c>
       <c r="H78" s="1">
-        <f>F78-C78</f>
-        <v/>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>SALE</t>
-        </is>
+        <f>IF(OR(F78="",C78=""),"",F78-C78)</f>
+        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Bronze head of a goddess, likely Venus (joint; EPGC share)</t>
+          <t>Roman Gold Belt</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -5076,10 +5078,10 @@
         </is>
       </c>
       <c r="C79" s="1" t="n">
-        <v>20000</v>
+        <v>45000</v>
       </c>
       <c r="F79" s="1" t="n">
-        <v>26000</v>
+        <v>50000</v>
       </c>
       <c r="H79" s="1">
         <f>F79-C79</f>
@@ -5087,14 +5089,14 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>SALE (joint, EPGC share)</t>
+          <t>SALE</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>August Fortuna joint — unnamed object (EPGC share)</t>
+          <t>Bronze head of a goddess, likely Venus (joint; EPGC share)</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -5106,7 +5108,7 @@
         <v>20000</v>
       </c>
       <c r="F80" s="1" t="n">
-        <v>25000</v>
+        <v>26000</v>
       </c>
       <c r="H80" s="1">
         <f>F80-C80</f>
@@ -5121,11 +5123,38 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>August Fortuna joint — unnamed object (EPGC share)</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Fortuna / Erdal Dere</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F81" s="1" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H81" s="1">
+        <f>F81-C81</f>
+        <v/>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>SALE (joint, EPGC share)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="H81" s="4">
-        <f>SUM(H51:H75)+H78+H79+H80</f>
+      <c r="H82" s="1">
+        <f>SUM(H51:H76)+H79+H80+H81</f>
         <v/>
       </c>
     </row>
